--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_22_36.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_22_36.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1367290.881612347</v>
+        <v>1361557.084860053</v>
       </c>
     </row>
     <row r="7">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11225139.03465134</v>
+        <v>11223948.89992745</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6645322.836910378</v>
+        <v>6645739.132417868</v>
       </c>
     </row>
     <row r="11">
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>6.876045741711209</v>
+        <v>6.876045741711437</v>
       </c>
       <c r="G2" t="n">
-        <v>15.30273751513482</v>
+        <v>15.30273751513505</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -22753,10 +22753,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>6.876045741711323</v>
+        <v>6.876045741711437</v>
       </c>
       <c r="G5" t="n">
-        <v>15.30273751513494</v>
+        <v>15.30273751513505</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -22990,10 +22990,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>6.876045741711323</v>
+        <v>6.876045741711437</v>
       </c>
       <c r="G8" t="n">
-        <v>15.30273751513494</v>
+        <v>15.30273751513505</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -23215,28 +23215,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>369.7338416634806</v>
+        <v>370.7845523088681</v>
       </c>
       <c r="C11" t="n">
-        <v>352.2728917710076</v>
+        <v>353.323602416395</v>
       </c>
       <c r="D11" t="n">
-        <v>341.683041620683</v>
+        <v>342.7337522660704</v>
       </c>
       <c r="E11" t="n">
-        <v>368.9303700722618</v>
+        <v>369.9810807176493</v>
       </c>
       <c r="F11" t="n">
-        <v>393.8760457417114</v>
+        <v>394.9267563870989</v>
       </c>
       <c r="G11" t="n">
-        <v>402.302737515135</v>
+        <v>403.3534481605225</v>
       </c>
       <c r="H11" t="n">
-        <v>326.4748021157671</v>
+        <v>327.5255127611546</v>
       </c>
       <c r="I11" t="n">
-        <v>197.4758895704059</v>
+        <v>198.5266002157934</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,28 +23263,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>136.8691179411497</v>
+        <v>137.9198285865372</v>
       </c>
       <c r="S11" t="n">
-        <v>196.0200695862453</v>
+        <v>197.0707802316328</v>
       </c>
       <c r="T11" t="n">
-        <v>210.0958495641314</v>
+        <v>211.1465602095188</v>
       </c>
       <c r="U11" t="n">
-        <v>238.3456529078365</v>
+        <v>239.396363553224</v>
       </c>
       <c r="V11" t="n">
-        <v>314.7522584701349</v>
+        <v>315.8029691155224</v>
       </c>
       <c r="W11" t="n">
-        <v>336.240968717413</v>
+        <v>337.2916793628005</v>
       </c>
       <c r="X11" t="n">
-        <v>356.731100678469</v>
+        <v>357.7818113238565</v>
       </c>
       <c r="Y11" t="n">
-        <v>373.2379386560536</v>
+        <v>374.2886493014411</v>
       </c>
     </row>
     <row r="12">
@@ -23294,28 +23294,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>153.5331836498673</v>
+        <v>154.5838942952548</v>
       </c>
       <c r="C12" t="n">
-        <v>159.7084989883157</v>
+        <v>160.7592096337032</v>
       </c>
       <c r="D12" t="n">
-        <v>134.4450655646388</v>
+        <v>135.4957762100262</v>
       </c>
       <c r="E12" t="n">
-        <v>144.6450804554009</v>
+        <v>145.6957911007884</v>
       </c>
       <c r="F12" t="n">
-        <v>132.0692123933839</v>
+        <v>133.1199230387714</v>
       </c>
       <c r="G12" t="n">
-        <v>124.3435171632106</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="H12" t="n">
-        <v>99.23544423649646</v>
+        <v>100.2861548818839</v>
       </c>
       <c r="I12" t="n">
-        <v>76.39663285141508</v>
+        <v>77.44734349680256</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,28 +23342,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>87.15783415264313</v>
+        <v>88.20854479803062</v>
       </c>
       <c r="S12" t="n">
-        <v>158.6831711038378</v>
+        <v>159.7338817492253</v>
       </c>
       <c r="T12" t="n">
-        <v>187.1647286948216</v>
+        <v>188.2154393402091</v>
       </c>
       <c r="U12" t="n">
-        <v>212.9413820809748</v>
+        <v>213.9920927263623</v>
       </c>
       <c r="V12" t="n">
-        <v>219.8005871494253</v>
+        <v>220.8512977948128</v>
       </c>
       <c r="W12" t="n">
-        <v>238.6949831609196</v>
+        <v>239.7456938063071</v>
       </c>
       <c r="X12" t="n">
-        <v>192.7729852034775</v>
+        <v>193.823695848865</v>
       </c>
       <c r="Y12" t="n">
-        <v>192.6826957773044</v>
+        <v>193.7334064226918</v>
       </c>
     </row>
     <row r="13">
@@ -23373,34 +23373,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>166.8319801819373</v>
+        <v>167.8826908273248</v>
       </c>
       <c r="C13" t="n">
-        <v>154.2468210986278</v>
+        <v>155.2975317440153</v>
       </c>
       <c r="D13" t="n">
-        <v>135.6154730182124</v>
+        <v>136.6661836635998</v>
       </c>
       <c r="E13" t="n">
-        <v>133.4339626465692</v>
+        <v>134.4846732919567</v>
       </c>
       <c r="F13" t="n">
-        <v>132.4210480229312</v>
+        <v>133.4717586683187</v>
       </c>
       <c r="G13" t="n">
-        <v>154.9909793584588</v>
+        <v>156.0416900038462</v>
       </c>
       <c r="H13" t="n">
-        <v>149.2271725074396</v>
+        <v>150.2778831528271</v>
       </c>
       <c r="I13" t="n">
-        <v>142.4504749272583</v>
+        <v>143.5011855726458</v>
       </c>
       <c r="J13" t="n">
-        <v>80.35918011667277</v>
+        <v>81.40989076206026</v>
       </c>
       <c r="K13" t="n">
-        <v>9.269491825882852</v>
+        <v>10.32020247127033</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23418,31 +23418,31 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>73.16204325169439</v>
+        <v>74.21275389708187</v>
       </c>
       <c r="R13" t="n">
-        <v>164.2933913771695</v>
+        <v>165.344102022557</v>
       </c>
       <c r="S13" t="n">
-        <v>211.0165980369723</v>
+        <v>212.0673086823597</v>
       </c>
       <c r="T13" t="n">
-        <v>214.9455894282815</v>
+        <v>215.996300073669</v>
       </c>
       <c r="U13" t="n">
-        <v>273.3190293564909</v>
+        <v>274.3697400018784</v>
       </c>
       <c r="V13" t="n">
-        <v>239.137643323828</v>
+        <v>240.1883539692155</v>
       </c>
       <c r="W13" t="n">
-        <v>273.522998336591</v>
+        <v>274.5737089819785</v>
       </c>
       <c r="X13" t="n">
-        <v>212.7096553890372</v>
+        <v>213.7603660344246</v>
       </c>
       <c r="Y13" t="n">
-        <v>205.5846533520948</v>
+        <v>206.6353639974823</v>
       </c>
     </row>
     <row r="14">
@@ -23452,28 +23452,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>289.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C14" t="n">
-        <v>272.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D14" t="n">
-        <v>261.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E14" t="n">
-        <v>288.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F14" t="n">
-        <v>313.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G14" t="n">
-        <v>322.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H14" t="n">
-        <v>246.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I14" t="n">
-        <v>117.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,28 +23500,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>56.8691179411497</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S14" t="n">
-        <v>116.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T14" t="n">
-        <v>130.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U14" t="n">
-        <v>158.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V14" t="n">
-        <v>234.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W14" t="n">
-        <v>256.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X14" t="n">
-        <v>276.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y14" t="n">
-        <v>293.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="15">
@@ -23531,25 +23531,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>73.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C15" t="n">
-        <v>79.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D15" t="n">
-        <v>54.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E15" t="n">
-        <v>64.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F15" t="n">
-        <v>52.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G15" t="n">
-        <v>44.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H15" t="n">
-        <v>19.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23579,28 +23579,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>7.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S15" t="n">
-        <v>78.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T15" t="n">
-        <v>107.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U15" t="n">
-        <v>132.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V15" t="n">
-        <v>139.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W15" t="n">
-        <v>158.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X15" t="n">
-        <v>112.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y15" t="n">
-        <v>112.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="16">
@@ -23610,31 +23610,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>86.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C16" t="n">
-        <v>74.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D16" t="n">
-        <v>55.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E16" t="n">
-        <v>53.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F16" t="n">
-        <v>52.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G16" t="n">
-        <v>74.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H16" t="n">
-        <v>69.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I16" t="n">
-        <v>62.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3591801166728017</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23658,28 +23658,28 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>84.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S16" t="n">
-        <v>131.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T16" t="n">
-        <v>134.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U16" t="n">
-        <v>193.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V16" t="n">
-        <v>159.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W16" t="n">
-        <v>193.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X16" t="n">
-        <v>132.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y16" t="n">
-        <v>125.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="17">
@@ -23689,28 +23689,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>289.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C17" t="n">
-        <v>272.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D17" t="n">
-        <v>261.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E17" t="n">
-        <v>288.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F17" t="n">
-        <v>313.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G17" t="n">
-        <v>322.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H17" t="n">
-        <v>246.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I17" t="n">
-        <v>117.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,28 +23737,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>56.8691179411497</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S17" t="n">
-        <v>116.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T17" t="n">
-        <v>130.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U17" t="n">
-        <v>158.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V17" t="n">
-        <v>234.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W17" t="n">
-        <v>256.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X17" t="n">
-        <v>276.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y17" t="n">
-        <v>293.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="18">
@@ -23768,25 +23768,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>73.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C18" t="n">
-        <v>79.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D18" t="n">
-        <v>54.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E18" t="n">
-        <v>64.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F18" t="n">
-        <v>52.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G18" t="n">
-        <v>44.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H18" t="n">
-        <v>19.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23816,28 +23816,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>7.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S18" t="n">
-        <v>78.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T18" t="n">
-        <v>107.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U18" t="n">
-        <v>132.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V18" t="n">
-        <v>139.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W18" t="n">
-        <v>158.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X18" t="n">
-        <v>112.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y18" t="n">
-        <v>112.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="19">
@@ -23847,31 +23847,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>86.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C19" t="n">
-        <v>74.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D19" t="n">
-        <v>55.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E19" t="n">
-        <v>53.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F19" t="n">
-        <v>52.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G19" t="n">
-        <v>74.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H19" t="n">
-        <v>69.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I19" t="n">
-        <v>62.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3591801166727677</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23895,28 +23895,28 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>84.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S19" t="n">
-        <v>131.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T19" t="n">
-        <v>134.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U19" t="n">
-        <v>193.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V19" t="n">
-        <v>159.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W19" t="n">
-        <v>193.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X19" t="n">
-        <v>132.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y19" t="n">
-        <v>125.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="20">
@@ -23926,28 +23926,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>289.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C20" t="n">
-        <v>272.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D20" t="n">
-        <v>261.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E20" t="n">
-        <v>288.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F20" t="n">
-        <v>313.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G20" t="n">
-        <v>322.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H20" t="n">
-        <v>246.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I20" t="n">
-        <v>117.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,28 +23974,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>56.8691179411497</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S20" t="n">
-        <v>116.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T20" t="n">
-        <v>130.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U20" t="n">
-        <v>158.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V20" t="n">
-        <v>234.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W20" t="n">
-        <v>256.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X20" t="n">
-        <v>276.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y20" t="n">
-        <v>293.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="21">
@@ -24005,25 +24005,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>73.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C21" t="n">
-        <v>79.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D21" t="n">
-        <v>54.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E21" t="n">
-        <v>64.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F21" t="n">
-        <v>52.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G21" t="n">
-        <v>44.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H21" t="n">
-        <v>19.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -24053,28 +24053,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>7.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S21" t="n">
-        <v>78.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T21" t="n">
-        <v>107.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U21" t="n">
-        <v>132.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V21" t="n">
-        <v>139.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W21" t="n">
-        <v>158.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X21" t="n">
-        <v>112.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y21" t="n">
-        <v>112.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="22">
@@ -24084,31 +24084,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>86.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C22" t="n">
-        <v>74.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D22" t="n">
-        <v>55.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E22" t="n">
-        <v>53.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F22" t="n">
-        <v>52.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G22" t="n">
-        <v>74.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H22" t="n">
-        <v>69.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I22" t="n">
-        <v>62.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3591801166728069</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24132,28 +24132,28 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>84.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S22" t="n">
-        <v>131.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T22" t="n">
-        <v>134.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U22" t="n">
-        <v>193.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V22" t="n">
-        <v>159.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W22" t="n">
-        <v>193.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X22" t="n">
-        <v>132.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y22" t="n">
-        <v>125.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="23">
@@ -24163,28 +24163,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>289.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C23" t="n">
-        <v>272.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D23" t="n">
-        <v>261.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E23" t="n">
-        <v>288.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F23" t="n">
-        <v>313.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G23" t="n">
-        <v>322.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H23" t="n">
-        <v>246.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I23" t="n">
-        <v>117.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,28 +24211,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>56.8691179411497</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S23" t="n">
-        <v>116.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T23" t="n">
-        <v>130.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U23" t="n">
-        <v>158.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V23" t="n">
-        <v>234.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W23" t="n">
-        <v>256.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X23" t="n">
-        <v>276.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y23" t="n">
-        <v>293.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="24">
@@ -24242,25 +24242,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>73.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C24" t="n">
-        <v>79.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D24" t="n">
-        <v>54.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E24" t="n">
-        <v>64.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F24" t="n">
-        <v>52.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G24" t="n">
-        <v>44.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H24" t="n">
-        <v>19.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -24290,28 +24290,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>7.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S24" t="n">
-        <v>78.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T24" t="n">
-        <v>107.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U24" t="n">
-        <v>132.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V24" t="n">
-        <v>139.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W24" t="n">
-        <v>158.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X24" t="n">
-        <v>112.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y24" t="n">
-        <v>112.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="25">
@@ -24321,31 +24321,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>86.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C25" t="n">
-        <v>74.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D25" t="n">
-        <v>55.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E25" t="n">
-        <v>53.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F25" t="n">
-        <v>52.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G25" t="n">
-        <v>74.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H25" t="n">
-        <v>69.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I25" t="n">
-        <v>62.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3591801166727464</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24369,28 +24369,28 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>84.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S25" t="n">
-        <v>131.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T25" t="n">
-        <v>134.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U25" t="n">
-        <v>193.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V25" t="n">
-        <v>159.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W25" t="n">
-        <v>193.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X25" t="n">
-        <v>132.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y25" t="n">
-        <v>125.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="26">
@@ -24400,28 +24400,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>294.7338416634806</v>
+        <v>293.3372088120655</v>
       </c>
       <c r="C26" t="n">
-        <v>277.2728917710076</v>
+        <v>275.8762589195925</v>
       </c>
       <c r="D26" t="n">
-        <v>266.683041620683</v>
+        <v>265.2864087692679</v>
       </c>
       <c r="E26" t="n">
-        <v>293.9303700722618</v>
+        <v>292.5337372208467</v>
       </c>
       <c r="F26" t="n">
-        <v>318.8760457417114</v>
+        <v>317.4794128902964</v>
       </c>
       <c r="G26" t="n">
-        <v>327.302737515135</v>
+        <v>325.90610466372</v>
       </c>
       <c r="H26" t="n">
-        <v>251.4748021157671</v>
+        <v>250.0781692643521</v>
       </c>
       <c r="I26" t="n">
-        <v>122.4758895704059</v>
+        <v>121.0792567189908</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,28 +24448,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>61.86911794114968</v>
+        <v>60.4724850897346</v>
       </c>
       <c r="S26" t="n">
-        <v>121.0200695862453</v>
+        <v>119.6234367348303</v>
       </c>
       <c r="T26" t="n">
-        <v>135.0958495641314</v>
+        <v>133.6992167127163</v>
       </c>
       <c r="U26" t="n">
-        <v>163.3456529078365</v>
+        <v>161.9490200564214</v>
       </c>
       <c r="V26" t="n">
-        <v>239.7522584701349</v>
+        <v>238.3556256187198</v>
       </c>
       <c r="W26" t="n">
-        <v>261.240968717413</v>
+        <v>259.8443358659979</v>
       </c>
       <c r="X26" t="n">
-        <v>281.731100678469</v>
+        <v>280.334467827054</v>
       </c>
       <c r="Y26" t="n">
-        <v>298.2379386560536</v>
+        <v>296.8413058046385</v>
       </c>
     </row>
     <row r="27">
@@ -24479,28 +24479,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>78.53318364986734</v>
+        <v>77.13655079845226</v>
       </c>
       <c r="C27" t="n">
-        <v>84.70849898831574</v>
+        <v>83.31186613690066</v>
       </c>
       <c r="D27" t="n">
-        <v>59.44506556463875</v>
+        <v>58.04843271322368</v>
       </c>
       <c r="E27" t="n">
-        <v>69.64508045540094</v>
+        <v>68.24844760398587</v>
       </c>
       <c r="F27" t="n">
-        <v>57.06921239338388</v>
+        <v>55.6725795419688</v>
       </c>
       <c r="G27" t="n">
-        <v>49.34351716321063</v>
+        <v>47.94688431179556</v>
       </c>
       <c r="H27" t="n">
-        <v>24.23544423649646</v>
+        <v>22.83881138508139</v>
       </c>
       <c r="I27" t="n">
-        <v>1.396632851415077</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,28 +24527,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>12.15783415264313</v>
+        <v>10.76120130122806</v>
       </c>
       <c r="S27" t="n">
-        <v>83.68317110383782</v>
+        <v>82.28653825242274</v>
       </c>
       <c r="T27" t="n">
-        <v>112.1647286948216</v>
+        <v>110.7680958434065</v>
       </c>
       <c r="U27" t="n">
-        <v>137.9413820809748</v>
+        <v>136.5447492295597</v>
       </c>
       <c r="V27" t="n">
-        <v>144.8005871494253</v>
+        <v>143.4039542980102</v>
       </c>
       <c r="W27" t="n">
-        <v>163.6949831609196</v>
+        <v>162.2983503095045</v>
       </c>
       <c r="X27" t="n">
-        <v>117.7729852034775</v>
+        <v>116.3763523520624</v>
       </c>
       <c r="Y27" t="n">
-        <v>117.6826957773044</v>
+        <v>116.2860629258893</v>
       </c>
     </row>
     <row r="28">
@@ -24558,31 +24558,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>91.8319801819373</v>
+        <v>90.43534733052222</v>
       </c>
       <c r="C28" t="n">
-        <v>79.24682109862783</v>
+        <v>77.85018824721276</v>
       </c>
       <c r="D28" t="n">
-        <v>60.61547301821236</v>
+        <v>59.21884016679728</v>
       </c>
       <c r="E28" t="n">
-        <v>58.43396264656917</v>
+        <v>57.03732979515409</v>
       </c>
       <c r="F28" t="n">
-        <v>57.42104802293125</v>
+        <v>56.02441517151617</v>
       </c>
       <c r="G28" t="n">
-        <v>79.99097935845876</v>
+        <v>78.59434650704368</v>
       </c>
       <c r="H28" t="n">
-        <v>74.22717250743958</v>
+        <v>72.8305396560245</v>
       </c>
       <c r="I28" t="n">
-        <v>67.45047492725828</v>
+        <v>66.05384207584321</v>
       </c>
       <c r="J28" t="n">
-        <v>5.359180116672775</v>
+        <v>3.962547265257697</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24606,28 +24606,28 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>89.29339137716948</v>
+        <v>87.89675852575441</v>
       </c>
       <c r="S28" t="n">
-        <v>136.0165980369723</v>
+        <v>134.6199651855572</v>
       </c>
       <c r="T28" t="n">
-        <v>139.9455894282815</v>
+        <v>138.5489565768664</v>
       </c>
       <c r="U28" t="n">
-        <v>198.3190293564909</v>
+        <v>196.9223965050758</v>
       </c>
       <c r="V28" t="n">
-        <v>164.137643323828</v>
+        <v>162.7410104724129</v>
       </c>
       <c r="W28" t="n">
-        <v>198.522998336591</v>
+        <v>197.1263654851759</v>
       </c>
       <c r="X28" t="n">
-        <v>137.7096553890372</v>
+        <v>136.3130225376221</v>
       </c>
       <c r="Y28" t="n">
-        <v>130.5846533520948</v>
+        <v>129.1880205006797</v>
       </c>
     </row>
     <row r="29">
@@ -24637,28 +24637,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>240.7338416634806</v>
+        <v>241.0693926669683</v>
       </c>
       <c r="C29" t="n">
-        <v>223.2728917710076</v>
+        <v>223.6084427744952</v>
       </c>
       <c r="D29" t="n">
-        <v>212.683041620683</v>
+        <v>213.0185926241707</v>
       </c>
       <c r="E29" t="n">
-        <v>239.9303700722618</v>
+        <v>240.2659210757495</v>
       </c>
       <c r="F29" t="n">
-        <v>264.8760457417114</v>
+        <v>265.2115967451991</v>
       </c>
       <c r="G29" t="n">
-        <v>273.302737515135</v>
+        <v>273.6382885186227</v>
       </c>
       <c r="H29" t="n">
-        <v>197.4748021157671</v>
+        <v>197.8103531192548</v>
       </c>
       <c r="I29" t="n">
-        <v>68.47588957040591</v>
+        <v>68.81144057389361</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,28 +24685,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>7.869117941149696</v>
+        <v>8.204668944637376</v>
       </c>
       <c r="S29" t="n">
-        <v>67.02006958624534</v>
+        <v>67.35562058973304</v>
       </c>
       <c r="T29" t="n">
-        <v>81.09584956413136</v>
+        <v>81.43140056761905</v>
       </c>
       <c r="U29" t="n">
-        <v>109.3456529078365</v>
+        <v>109.6812039113242</v>
       </c>
       <c r="V29" t="n">
-        <v>185.7522584701349</v>
+        <v>186.0878094736226</v>
       </c>
       <c r="W29" t="n">
-        <v>207.240968717413</v>
+        <v>207.5765197209007</v>
       </c>
       <c r="X29" t="n">
-        <v>227.731100678469</v>
+        <v>228.0666516819567</v>
       </c>
       <c r="Y29" t="n">
-        <v>244.2379386560536</v>
+        <v>244.5734896595413</v>
       </c>
     </row>
     <row r="30">
@@ -24716,19 +24716,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24.53318364986734</v>
+        <v>24.86873465335503</v>
       </c>
       <c r="C30" t="n">
-        <v>30.70849898831574</v>
+        <v>31.04404999180343</v>
       </c>
       <c r="D30" t="n">
-        <v>5.445065564638753</v>
+        <v>5.780616568126447</v>
       </c>
       <c r="E30" t="n">
-        <v>15.64508045540094</v>
+        <v>15.98063145888864</v>
       </c>
       <c r="F30" t="n">
-        <v>3.069212393383879</v>
+        <v>3.404763396871573</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -24767,25 +24767,25 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>29.68317110383782</v>
+        <v>30.01872210732552</v>
       </c>
       <c r="T30" t="n">
-        <v>58.1647286948216</v>
+        <v>58.5002796983093</v>
       </c>
       <c r="U30" t="n">
-        <v>83.94138208097482</v>
+        <v>84.27693308446251</v>
       </c>
       <c r="V30" t="n">
-        <v>90.80058714942527</v>
+        <v>91.13613815291296</v>
       </c>
       <c r="W30" t="n">
-        <v>109.6949831609196</v>
+        <v>110.0305341644073</v>
       </c>
       <c r="X30" t="n">
-        <v>63.77298520347748</v>
+        <v>64.10853620696517</v>
       </c>
       <c r="Y30" t="n">
-        <v>63.68269577730436</v>
+        <v>64.01824678079205</v>
       </c>
     </row>
     <row r="31">
@@ -24795,28 +24795,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>37.8319801819373</v>
+        <v>38.16753118542499</v>
       </c>
       <c r="C31" t="n">
-        <v>25.24682109862783</v>
+        <v>25.58237210211553</v>
       </c>
       <c r="D31" t="n">
-        <v>6.615473018212356</v>
+        <v>6.95102402170005</v>
       </c>
       <c r="E31" t="n">
-        <v>4.433962646569171</v>
+        <v>4.769513650056865</v>
       </c>
       <c r="F31" t="n">
-        <v>3.421048022931245</v>
+        <v>3.75659902641894</v>
       </c>
       <c r="G31" t="n">
-        <v>25.99097935845876</v>
+        <v>26.32653036194645</v>
       </c>
       <c r="H31" t="n">
-        <v>20.22717250743958</v>
+        <v>20.56272351092727</v>
       </c>
       <c r="I31" t="n">
-        <v>13.45047492725828</v>
+        <v>13.78602593074598</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -24843,28 +24843,28 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>35.29339137716948</v>
+        <v>35.62894238065718</v>
       </c>
       <c r="S31" t="n">
-        <v>82.01659803697225</v>
+        <v>82.35214904045995</v>
       </c>
       <c r="T31" t="n">
-        <v>85.94558942828149</v>
+        <v>86.28114043176919</v>
       </c>
       <c r="U31" t="n">
-        <v>144.3190293564909</v>
+        <v>144.6545803599786</v>
       </c>
       <c r="V31" t="n">
-        <v>110.137643323828</v>
+        <v>110.4731943273157</v>
       </c>
       <c r="W31" t="n">
-        <v>144.522998336591</v>
+        <v>144.8585493400787</v>
       </c>
       <c r="X31" t="n">
-        <v>83.70965538903715</v>
+        <v>84.04520639252485</v>
       </c>
       <c r="Y31" t="n">
-        <v>76.58465335209479</v>
+        <v>76.92020435558248</v>
       </c>
     </row>
     <row r="32">
@@ -24874,28 +24874,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>240.7338416634806</v>
+        <v>241.0693926669683</v>
       </c>
       <c r="C32" t="n">
-        <v>223.2728917710076</v>
+        <v>223.6084427744952</v>
       </c>
       <c r="D32" t="n">
-        <v>212.683041620683</v>
+        <v>213.0185926241707</v>
       </c>
       <c r="E32" t="n">
-        <v>239.9303700722618</v>
+        <v>240.2659210757495</v>
       </c>
       <c r="F32" t="n">
-        <v>264.8760457417114</v>
+        <v>265.2115967451991</v>
       </c>
       <c r="G32" t="n">
-        <v>273.302737515135</v>
+        <v>273.6382885186227</v>
       </c>
       <c r="H32" t="n">
-        <v>197.4748021157671</v>
+        <v>197.8103531192548</v>
       </c>
       <c r="I32" t="n">
-        <v>68.47588957040591</v>
+        <v>68.81144057389361</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,28 +24922,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>7.869117941149696</v>
+        <v>8.204668944637376</v>
       </c>
       <c r="S32" t="n">
-        <v>67.02006958624534</v>
+        <v>67.35562058973304</v>
       </c>
       <c r="T32" t="n">
-        <v>81.09584956413136</v>
+        <v>81.43140056761905</v>
       </c>
       <c r="U32" t="n">
-        <v>109.3456529078365</v>
+        <v>109.6812039113242</v>
       </c>
       <c r="V32" t="n">
-        <v>185.7522584701349</v>
+        <v>186.0878094736226</v>
       </c>
       <c r="W32" t="n">
-        <v>207.240968717413</v>
+        <v>207.5765197209007</v>
       </c>
       <c r="X32" t="n">
-        <v>227.731100678469</v>
+        <v>228.0666516819567</v>
       </c>
       <c r="Y32" t="n">
-        <v>244.2379386560536</v>
+        <v>244.5734896595413</v>
       </c>
     </row>
     <row r="33">
@@ -24953,19 +24953,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>24.53318364986734</v>
+        <v>24.86873465335503</v>
       </c>
       <c r="C33" t="n">
-        <v>30.70849898831574</v>
+        <v>31.04404999180343</v>
       </c>
       <c r="D33" t="n">
-        <v>5.445065564638753</v>
+        <v>5.780616568126447</v>
       </c>
       <c r="E33" t="n">
-        <v>15.64508045540094</v>
+        <v>15.98063145888864</v>
       </c>
       <c r="F33" t="n">
-        <v>3.069212393383879</v>
+        <v>3.404763396871573</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -25004,25 +25004,25 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>29.68317110383782</v>
+        <v>30.01872210732552</v>
       </c>
       <c r="T33" t="n">
-        <v>58.1647286948216</v>
+        <v>58.5002796983093</v>
       </c>
       <c r="U33" t="n">
-        <v>83.94138208097482</v>
+        <v>84.27693308446251</v>
       </c>
       <c r="V33" t="n">
-        <v>90.80058714942527</v>
+        <v>91.13613815291296</v>
       </c>
       <c r="W33" t="n">
-        <v>109.6949831609196</v>
+        <v>110.0305341644073</v>
       </c>
       <c r="X33" t="n">
-        <v>63.77298520347748</v>
+        <v>64.10853620696517</v>
       </c>
       <c r="Y33" t="n">
-        <v>63.68269577730436</v>
+        <v>64.01824678079205</v>
       </c>
     </row>
     <row r="34">
@@ -25032,28 +25032,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>37.8319801819373</v>
+        <v>38.16753118542499</v>
       </c>
       <c r="C34" t="n">
-        <v>25.24682109862783</v>
+        <v>25.58237210211553</v>
       </c>
       <c r="D34" t="n">
-        <v>6.615473018212356</v>
+        <v>6.95102402170005</v>
       </c>
       <c r="E34" t="n">
-        <v>4.433962646569171</v>
+        <v>4.769513650056865</v>
       </c>
       <c r="F34" t="n">
-        <v>3.421048022931245</v>
+        <v>3.75659902641894</v>
       </c>
       <c r="G34" t="n">
-        <v>25.99097935845876</v>
+        <v>26.32653036194645</v>
       </c>
       <c r="H34" t="n">
-        <v>20.22717250743958</v>
+        <v>20.56272351092727</v>
       </c>
       <c r="I34" t="n">
-        <v>13.45047492725828</v>
+        <v>13.78602593074598</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -25080,28 +25080,28 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>35.29339137716948</v>
+        <v>35.62894238065718</v>
       </c>
       <c r="S34" t="n">
-        <v>82.01659803697225</v>
+        <v>82.35214904045995</v>
       </c>
       <c r="T34" t="n">
-        <v>85.94558942828149</v>
+        <v>86.28114043176919</v>
       </c>
       <c r="U34" t="n">
-        <v>144.3190293564909</v>
+        <v>144.6545803599786</v>
       </c>
       <c r="V34" t="n">
-        <v>110.137643323828</v>
+        <v>110.4731943273157</v>
       </c>
       <c r="W34" t="n">
-        <v>144.522998336591</v>
+        <v>144.8585493400787</v>
       </c>
       <c r="X34" t="n">
-        <v>83.70965538903715</v>
+        <v>84.04520639252485</v>
       </c>
       <c r="Y34" t="n">
-        <v>76.58465335209479</v>
+        <v>76.92020435558248</v>
       </c>
     </row>
     <row r="35">
@@ -25111,28 +25111,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>240.7338416634806</v>
+        <v>241.0693926669683</v>
       </c>
       <c r="C35" t="n">
-        <v>223.2728917710076</v>
+        <v>223.6084427744952</v>
       </c>
       <c r="D35" t="n">
-        <v>212.683041620683</v>
+        <v>213.0185926241707</v>
       </c>
       <c r="E35" t="n">
-        <v>239.9303700722618</v>
+        <v>240.2659210757495</v>
       </c>
       <c r="F35" t="n">
-        <v>264.8760457417114</v>
+        <v>265.2115967451991</v>
       </c>
       <c r="G35" t="n">
-        <v>273.302737515135</v>
+        <v>273.6382885186227</v>
       </c>
       <c r="H35" t="n">
-        <v>197.4748021157671</v>
+        <v>197.8103531192548</v>
       </c>
       <c r="I35" t="n">
-        <v>68.47588957040591</v>
+        <v>68.81144057389361</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,28 +25159,28 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>7.869117941149696</v>
+        <v>8.204668944637376</v>
       </c>
       <c r="S35" t="n">
-        <v>67.02006958624534</v>
+        <v>67.35562058973304</v>
       </c>
       <c r="T35" t="n">
-        <v>81.09584956413136</v>
+        <v>81.43140056761905</v>
       </c>
       <c r="U35" t="n">
-        <v>109.3456529078365</v>
+        <v>109.6812039113242</v>
       </c>
       <c r="V35" t="n">
-        <v>185.7522584701349</v>
+        <v>186.0878094736226</v>
       </c>
       <c r="W35" t="n">
-        <v>207.240968717413</v>
+        <v>207.5765197209007</v>
       </c>
       <c r="X35" t="n">
-        <v>227.731100678469</v>
+        <v>228.0666516819567</v>
       </c>
       <c r="Y35" t="n">
-        <v>244.2379386560536</v>
+        <v>244.5734896595413</v>
       </c>
     </row>
     <row r="36">
@@ -25190,19 +25190,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>24.53318364986734</v>
+        <v>24.86873465335503</v>
       </c>
       <c r="C36" t="n">
-        <v>30.70849898831574</v>
+        <v>31.04404999180343</v>
       </c>
       <c r="D36" t="n">
-        <v>5.445065564638753</v>
+        <v>5.780616568126447</v>
       </c>
       <c r="E36" t="n">
-        <v>15.64508045540094</v>
+        <v>15.98063145888864</v>
       </c>
       <c r="F36" t="n">
-        <v>3.069212393383879</v>
+        <v>3.404763396871573</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -25241,25 +25241,25 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>29.68317110383782</v>
+        <v>30.01872210732552</v>
       </c>
       <c r="T36" t="n">
-        <v>58.1647286948216</v>
+        <v>58.5002796983093</v>
       </c>
       <c r="U36" t="n">
-        <v>83.94138208097482</v>
+        <v>84.27693308446251</v>
       </c>
       <c r="V36" t="n">
-        <v>90.80058714942527</v>
+        <v>91.13613815291296</v>
       </c>
       <c r="W36" t="n">
-        <v>109.6949831609196</v>
+        <v>110.0305341644073</v>
       </c>
       <c r="X36" t="n">
-        <v>63.77298520347748</v>
+        <v>64.10853620696517</v>
       </c>
       <c r="Y36" t="n">
-        <v>63.68269577730436</v>
+        <v>64.01824678079205</v>
       </c>
     </row>
     <row r="37">
@@ -25269,28 +25269,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>37.8319801819373</v>
+        <v>38.16753118542499</v>
       </c>
       <c r="C37" t="n">
-        <v>25.24682109862783</v>
+        <v>25.58237210211553</v>
       </c>
       <c r="D37" t="n">
-        <v>6.615473018212356</v>
+        <v>6.95102402170005</v>
       </c>
       <c r="E37" t="n">
-        <v>4.433962646569171</v>
+        <v>4.769513650056865</v>
       </c>
       <c r="F37" t="n">
-        <v>3.421048022931245</v>
+        <v>3.75659902641894</v>
       </c>
       <c r="G37" t="n">
-        <v>25.99097935845876</v>
+        <v>26.32653036194645</v>
       </c>
       <c r="H37" t="n">
-        <v>20.22717250743958</v>
+        <v>20.56272351092727</v>
       </c>
       <c r="I37" t="n">
-        <v>13.45047492725828</v>
+        <v>13.78602593074598</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -25317,28 +25317,28 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>35.29339137716948</v>
+        <v>35.62894238065718</v>
       </c>
       <c r="S37" t="n">
-        <v>82.01659803697225</v>
+        <v>82.35214904045995</v>
       </c>
       <c r="T37" t="n">
-        <v>85.94558942828149</v>
+        <v>86.28114043176919</v>
       </c>
       <c r="U37" t="n">
-        <v>144.3190293564909</v>
+        <v>144.6545803599786</v>
       </c>
       <c r="V37" t="n">
-        <v>110.137643323828</v>
+        <v>110.4731943273157</v>
       </c>
       <c r="W37" t="n">
-        <v>144.522998336591</v>
+        <v>144.8585493400787</v>
       </c>
       <c r="X37" t="n">
-        <v>83.70965538903715</v>
+        <v>84.04520639252485</v>
       </c>
       <c r="Y37" t="n">
-        <v>76.58465335209479</v>
+        <v>76.92020435558248</v>
       </c>
     </row>
     <row r="38">
@@ -25348,28 +25348,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>240.7338416634806</v>
+        <v>241.0693926669683</v>
       </c>
       <c r="C38" t="n">
-        <v>223.2728917710076</v>
+        <v>223.6084427744952</v>
       </c>
       <c r="D38" t="n">
-        <v>212.683041620683</v>
+        <v>213.0185926241707</v>
       </c>
       <c r="E38" t="n">
-        <v>239.9303700722618</v>
+        <v>240.2659210757495</v>
       </c>
       <c r="F38" t="n">
-        <v>264.8760457417114</v>
+        <v>265.2115967451991</v>
       </c>
       <c r="G38" t="n">
-        <v>273.302737515135</v>
+        <v>273.6382885186227</v>
       </c>
       <c r="H38" t="n">
-        <v>197.4748021157671</v>
+        <v>197.8103531192548</v>
       </c>
       <c r="I38" t="n">
-        <v>68.47588957040591</v>
+        <v>68.81144057389361</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,28 +25396,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>7.869117941149682</v>
+        <v>8.204668944637376</v>
       </c>
       <c r="S38" t="n">
-        <v>67.02006958624534</v>
+        <v>67.35562058973304</v>
       </c>
       <c r="T38" t="n">
-        <v>81.09584956413136</v>
+        <v>81.43140056761905</v>
       </c>
       <c r="U38" t="n">
-        <v>109.3456529078365</v>
+        <v>109.6812039113242</v>
       </c>
       <c r="V38" t="n">
-        <v>185.7522584701349</v>
+        <v>186.0878094736226</v>
       </c>
       <c r="W38" t="n">
-        <v>207.240968717413</v>
+        <v>207.5765197209007</v>
       </c>
       <c r="X38" t="n">
-        <v>227.731100678469</v>
+        <v>228.0666516819567</v>
       </c>
       <c r="Y38" t="n">
-        <v>244.2379386560536</v>
+        <v>244.5734896595413</v>
       </c>
     </row>
     <row r="39">
@@ -25427,19 +25427,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>24.53318364986734</v>
+        <v>24.86873465335503</v>
       </c>
       <c r="C39" t="n">
-        <v>30.70849898831574</v>
+        <v>31.04404999180343</v>
       </c>
       <c r="D39" t="n">
-        <v>5.445065564638753</v>
+        <v>5.780616568126447</v>
       </c>
       <c r="E39" t="n">
-        <v>15.64508045540094</v>
+        <v>15.98063145888864</v>
       </c>
       <c r="F39" t="n">
-        <v>3.069212393383879</v>
+        <v>3.404763396871573</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -25478,25 +25478,25 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>29.68317110383782</v>
+        <v>30.01872210732552</v>
       </c>
       <c r="T39" t="n">
-        <v>58.1647286948216</v>
+        <v>58.5002796983093</v>
       </c>
       <c r="U39" t="n">
-        <v>83.94138208097482</v>
+        <v>84.27693308446251</v>
       </c>
       <c r="V39" t="n">
-        <v>90.80058714942527</v>
+        <v>91.13613815291296</v>
       </c>
       <c r="W39" t="n">
-        <v>109.6949831609196</v>
+        <v>110.0305341644073</v>
       </c>
       <c r="X39" t="n">
-        <v>63.77298520347748</v>
+        <v>64.10853620696517</v>
       </c>
       <c r="Y39" t="n">
-        <v>63.68269577730436</v>
+        <v>64.01824678079205</v>
       </c>
     </row>
     <row r="40">
@@ -25506,28 +25506,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>37.8319801819373</v>
+        <v>38.16753118542499</v>
       </c>
       <c r="C40" t="n">
-        <v>25.24682109862783</v>
+        <v>25.58237210211553</v>
       </c>
       <c r="D40" t="n">
-        <v>6.615473018212356</v>
+        <v>6.95102402170005</v>
       </c>
       <c r="E40" t="n">
-        <v>4.433962646569171</v>
+        <v>4.769513650056865</v>
       </c>
       <c r="F40" t="n">
-        <v>3.421048022931245</v>
+        <v>3.75659902641894</v>
       </c>
       <c r="G40" t="n">
-        <v>25.99097935845876</v>
+        <v>26.32653036194645</v>
       </c>
       <c r="H40" t="n">
-        <v>20.22717250743958</v>
+        <v>20.56272351092727</v>
       </c>
       <c r="I40" t="n">
-        <v>13.45047492725828</v>
+        <v>13.78602593074598</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -25554,28 +25554,28 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>35.29339137716948</v>
+        <v>35.62894238065718</v>
       </c>
       <c r="S40" t="n">
-        <v>82.01659803697225</v>
+        <v>82.35214904045995</v>
       </c>
       <c r="T40" t="n">
-        <v>85.94558942828149</v>
+        <v>86.28114043176919</v>
       </c>
       <c r="U40" t="n">
-        <v>144.3190293564909</v>
+        <v>144.6545803599786</v>
       </c>
       <c r="V40" t="n">
-        <v>110.137643323828</v>
+        <v>110.4731943273157</v>
       </c>
       <c r="W40" t="n">
-        <v>144.522998336591</v>
+        <v>144.8585493400787</v>
       </c>
       <c r="X40" t="n">
-        <v>83.70965538903715</v>
+        <v>84.04520639252485</v>
       </c>
       <c r="Y40" t="n">
-        <v>76.58465335209479</v>
+        <v>76.92020435558248</v>
       </c>
     </row>
     <row r="41">
@@ -25585,28 +25585,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>248.7338416634806</v>
+        <v>249.0561347563231</v>
       </c>
       <c r="C41" t="n">
-        <v>231.2728917710076</v>
+        <v>231.5951848638501</v>
       </c>
       <c r="D41" t="n">
-        <v>220.683041620683</v>
+        <v>221.0053347135255</v>
       </c>
       <c r="E41" t="n">
-        <v>247.9303700722618</v>
+        <v>248.2526631651043</v>
       </c>
       <c r="F41" t="n">
-        <v>272.8760457417114</v>
+        <v>273.198338834554</v>
       </c>
       <c r="G41" t="n">
-        <v>281.302737515135</v>
+        <v>281.6250306079776</v>
       </c>
       <c r="H41" t="n">
-        <v>205.4748021157671</v>
+        <v>205.7970952086096</v>
       </c>
       <c r="I41" t="n">
-        <v>76.47588957040591</v>
+        <v>76.79818266324841</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,28 +25633,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>15.86911794114968</v>
+        <v>16.19141103399218</v>
       </c>
       <c r="S41" t="n">
-        <v>75.02006958624534</v>
+        <v>75.34236267908784</v>
       </c>
       <c r="T41" t="n">
-        <v>89.09584956413136</v>
+        <v>89.41814265697386</v>
       </c>
       <c r="U41" t="n">
-        <v>117.3456529078365</v>
+        <v>117.667946000679</v>
       </c>
       <c r="V41" t="n">
-        <v>193.7522584701349</v>
+        <v>194.0745515629774</v>
       </c>
       <c r="W41" t="n">
-        <v>215.240968717413</v>
+        <v>215.5632618102555</v>
       </c>
       <c r="X41" t="n">
-        <v>235.731100678469</v>
+        <v>236.0533937713115</v>
       </c>
       <c r="Y41" t="n">
-        <v>252.2379386560536</v>
+        <v>252.5602317488961</v>
       </c>
     </row>
     <row r="42">
@@ -25664,22 +25664,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>32.53318364986734</v>
+        <v>32.85547674270984</v>
       </c>
       <c r="C42" t="n">
-        <v>38.70849898831574</v>
+        <v>39.03079208115824</v>
       </c>
       <c r="D42" t="n">
-        <v>13.44506556463875</v>
+        <v>13.76735865748125</v>
       </c>
       <c r="E42" t="n">
-        <v>23.64508045540094</v>
+        <v>23.96737354824344</v>
       </c>
       <c r="F42" t="n">
-        <v>11.06921239338388</v>
+        <v>11.39150548622638</v>
       </c>
       <c r="G42" t="n">
-        <v>3.343517163210635</v>
+        <v>3.665810256053135</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -25715,25 +25715,25 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>37.68317110383782</v>
+        <v>38.00546419668032</v>
       </c>
       <c r="T42" t="n">
-        <v>66.1647286948216</v>
+        <v>66.4870217876641</v>
       </c>
       <c r="U42" t="n">
-        <v>91.94138208097482</v>
+        <v>92.26367517381732</v>
       </c>
       <c r="V42" t="n">
-        <v>98.80058714942527</v>
+        <v>99.12288024226777</v>
       </c>
       <c r="W42" t="n">
-        <v>117.6949831609196</v>
+        <v>118.0172762537621</v>
       </c>
       <c r="X42" t="n">
-        <v>71.77298520347748</v>
+        <v>72.09527829631998</v>
       </c>
       <c r="Y42" t="n">
-        <v>71.68269577730436</v>
+        <v>72.00498887014686</v>
       </c>
     </row>
     <row r="43">
@@ -25743,28 +25743,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>45.8319801819373</v>
+        <v>46.1542732747798</v>
       </c>
       <c r="C43" t="n">
-        <v>33.24682109862783</v>
+        <v>33.56911419147033</v>
       </c>
       <c r="D43" t="n">
-        <v>14.61547301821236</v>
+        <v>14.93776611105486</v>
       </c>
       <c r="E43" t="n">
-        <v>12.43396264656917</v>
+        <v>12.75625573941167</v>
       </c>
       <c r="F43" t="n">
-        <v>11.42104802293125</v>
+        <v>11.74334111577375</v>
       </c>
       <c r="G43" t="n">
-        <v>33.99097935845876</v>
+        <v>34.31327245130126</v>
       </c>
       <c r="H43" t="n">
-        <v>28.22717250743958</v>
+        <v>28.54946560028208</v>
       </c>
       <c r="I43" t="n">
-        <v>21.45047492725828</v>
+        <v>21.77276802010078</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -25791,28 +25791,28 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>43.29339137716948</v>
+        <v>43.61568447001198</v>
       </c>
       <c r="S43" t="n">
-        <v>90.01659803697225</v>
+        <v>90.33889112981475</v>
       </c>
       <c r="T43" t="n">
-        <v>93.94558942828149</v>
+        <v>94.26788252112399</v>
       </c>
       <c r="U43" t="n">
-        <v>152.3190293564909</v>
+        <v>152.6413224493334</v>
       </c>
       <c r="V43" t="n">
-        <v>118.137643323828</v>
+        <v>118.4599364166705</v>
       </c>
       <c r="W43" t="n">
-        <v>152.522998336591</v>
+        <v>152.8452914294335</v>
       </c>
       <c r="X43" t="n">
-        <v>91.70965538903715</v>
+        <v>92.03194848187965</v>
       </c>
       <c r="Y43" t="n">
-        <v>84.58465335209479</v>
+        <v>84.90694644493729</v>
       </c>
     </row>
     <row r="44">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>329196.0196570338</v>
+        <v>327045.4251080545</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>491227.7576205813</v>
+        <v>491935.328083222</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>491227.7576205813</v>
+        <v>491935.328083222</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>491227.7576205813</v>
+        <v>491935.328083222</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>491227.7576205813</v>
+        <v>491935.328083222</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>481327.6229726162</v>
+        <v>484129.2684725548</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>584014.9990066682</v>
+        <v>583397.101966806</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>584014.9990066682</v>
+        <v>583397.101966806</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>584014.9990066682</v>
+        <v>583397.101966806</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>584014.9990066682</v>
+        <v>583397.101966806</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>569162.9786481061</v>
+        <v>568557.8798121561</v>
       </c>
     </row>
     <row r="16">
@@ -26261,46 +26261,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>737348.7048453355</v>
+        <v>737348.7048453346</v>
       </c>
       <c r="C2" t="n">
-        <v>737348.7048453358</v>
+        <v>737348.7048453348</v>
       </c>
       <c r="D2" t="n">
-        <v>737348.7048453346</v>
+        <v>737348.7048453344</v>
       </c>
       <c r="E2" t="n">
-        <v>223345.9837825862</v>
+        <v>221068.8836719024</v>
       </c>
       <c r="F2" t="n">
-        <v>394909.0004498719</v>
+        <v>395658.1927044326</v>
       </c>
       <c r="G2" t="n">
-        <v>394909.0004498719</v>
+        <v>395658.1927044327</v>
       </c>
       <c r="H2" t="n">
-        <v>394909.0004498719</v>
+        <v>395658.1927044325</v>
       </c>
       <c r="I2" t="n">
-        <v>394909.0004498719</v>
+        <v>395658.1927044325</v>
       </c>
       <c r="J2" t="n">
-        <v>384426.5049402619</v>
+        <v>387392.9531166674</v>
       </c>
       <c r="K2" t="n">
-        <v>493154.3148586698</v>
+        <v>492500.0709341094</v>
       </c>
       <c r="L2" t="n">
-        <v>493154.3148586697</v>
+        <v>492500.0709341094</v>
       </c>
       <c r="M2" t="n">
-        <v>493154.3148586698</v>
+        <v>492500.0709341094</v>
       </c>
       <c r="N2" t="n">
-        <v>493154.3148586697</v>
+        <v>492500.0709341094</v>
       </c>
       <c r="O2" t="n">
-        <v>477428.6462437221</v>
+        <v>476787.9533585975</v>
       </c>
       <c r="P2" t="n">
         <v>193513.3299566035</v>
@@ -26322,10 +26322,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>10400</v>
+        <v>9559.431483690014</v>
       </c>
       <c r="F3" t="n">
-        <v>64000</v>
+        <v>65127.91260964821</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -26337,10 +26337,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>6400</v>
+        <v>6389.393671483856</v>
       </c>
       <c r="K3" t="n">
-        <v>107200</v>
+        <v>106942.165525726</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>463150.7311021102</v>
+        <v>463844.3331297129</v>
       </c>
       <c r="C4" t="n">
-        <v>463150.7311021105</v>
+        <v>463844.333129713</v>
       </c>
       <c r="D4" t="n">
-        <v>463150.7311021099</v>
+        <v>463844.3331297129</v>
       </c>
       <c r="E4" t="n">
-        <v>137177.5867298067</v>
+        <v>136427.0845674644</v>
       </c>
       <c r="F4" t="n">
-        <v>245980.3881729644</v>
+        <v>247149.1171696497</v>
       </c>
       <c r="G4" t="n">
-        <v>245980.3881729644</v>
+        <v>247149.1171696497</v>
       </c>
       <c r="H4" t="n">
-        <v>245980.3881729644</v>
+        <v>247149.1171696497</v>
       </c>
       <c r="I4" t="n">
-        <v>245980.3881729644</v>
+        <v>247149.1171696497</v>
       </c>
       <c r="J4" t="n">
-        <v>239332.5400544347</v>
+        <v>241907.4209158952</v>
       </c>
       <c r="K4" t="n">
-        <v>308286.1557211711</v>
+        <v>308564.8456470749</v>
       </c>
       <c r="L4" t="n">
-        <v>308286.1557211712</v>
+        <v>308564.8456470749</v>
       </c>
       <c r="M4" t="n">
-        <v>308286.1557211711</v>
+        <v>308564.8456470749</v>
       </c>
       <c r="N4" t="n">
-        <v>308286.1557211712</v>
+        <v>308564.8456470749</v>
       </c>
       <c r="O4" t="n">
-        <v>298313.1625137175</v>
+        <v>298600.4463142326</v>
       </c>
       <c r="P4" t="n">
-        <v>118258.146084591</v>
+        <v>118951.7481121942</v>
       </c>
     </row>
     <row r="5">
@@ -26426,37 +26426,37 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1092.897</v>
+        <v>1004.56480675292</v>
       </c>
       <c r="F5" t="n">
-        <v>7818.417</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="G5" t="n">
-        <v>7818.417</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="H5" t="n">
-        <v>7818.417</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="I5" t="n">
-        <v>7818.417</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="J5" t="n">
-        <v>7398.072</v>
+        <v>7515.485527185614</v>
       </c>
       <c r="K5" t="n">
-        <v>11937.798</v>
+        <v>11909.58856268779</v>
       </c>
       <c r="L5" t="n">
-        <v>11937.798</v>
+        <v>11909.58856268779</v>
       </c>
       <c r="M5" t="n">
-        <v>11937.798</v>
+        <v>11909.58856268779</v>
       </c>
       <c r="N5" t="n">
-        <v>11937.798</v>
+        <v>11909.58856268779</v>
       </c>
       <c r="O5" t="n">
-        <v>11265.246</v>
+        <v>11238.15114197782</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>240570.3737432252</v>
+        <v>239876.7717156217</v>
       </c>
       <c r="C6" t="n">
-        <v>240570.3737432253</v>
+        <v>239876.7717156218</v>
       </c>
       <c r="D6" t="n">
-        <v>240570.3737432247</v>
+        <v>239876.7717156215</v>
       </c>
       <c r="E6" t="n">
-        <v>74675.50005277953</v>
+        <v>74077.80281399511</v>
       </c>
       <c r="F6" t="n">
-        <v>77110.19527690749</v>
+        <v>75532.55001190619</v>
       </c>
       <c r="G6" t="n">
-        <v>141110.1952769075</v>
+        <v>140660.4626215544</v>
       </c>
       <c r="H6" t="n">
-        <v>141110.1952769075</v>
+        <v>140660.4626215542</v>
       </c>
       <c r="I6" t="n">
-        <v>141110.1952769076</v>
+        <v>140660.4626215542</v>
       </c>
       <c r="J6" t="n">
-        <v>131295.8928858272</v>
+        <v>131580.6530021027</v>
       </c>
       <c r="K6" t="n">
-        <v>65730.36113749865</v>
+        <v>65083.47119862075</v>
       </c>
       <c r="L6" t="n">
-        <v>172930.3611374985</v>
+        <v>172025.6367243467</v>
       </c>
       <c r="M6" t="n">
-        <v>172930.3611374987</v>
+        <v>172025.6367243468</v>
       </c>
       <c r="N6" t="n">
-        <v>172930.3611374985</v>
+        <v>172025.6367243468</v>
       </c>
       <c r="O6" t="n">
-        <v>167850.2377300045</v>
+        <v>166949.3559023871</v>
       </c>
       <c r="P6" t="n">
-        <v>75255.18387201247</v>
+        <v>74561.58184440932</v>
       </c>
     </row>
   </sheetData>
@@ -26632,37 +26632,37 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F2" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G2" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H2" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I2" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J2" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K2" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="L2" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="M2" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="N2" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="O2" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -26849,31 +26849,31 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>81.40989076206026</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>7.98674208935482</v>
       </c>
       <c r="K2" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -26953,13 +26953,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -26968,25 +26968,25 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27081,10 +27081,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K2" t="n">
-        <v>80</v>
+        <v>81.40989076206026</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27096,10 +27096,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>7.98674208935482</v>
       </c>
       <c r="P2" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
     </row>
     <row r="3">
@@ -27301,28 +27301,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>382.7338416634813</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C2" t="n">
-        <v>365.2728917710083</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D2" t="n">
-        <v>354.6830416206834</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E2" t="n">
-        <v>381.9303700722625</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F2" t="n">
-        <v>400.0000000000002</v>
+        <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>400.0000000000002</v>
+        <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>339.4748021157676</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I2" t="n">
-        <v>210.4758895704061</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J2" t="n">
         <v>11.94928935461252</v>
@@ -27352,25 +27352,25 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S2" t="n">
-        <v>209.0200695862455</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T2" t="n">
-        <v>223.0958495641318</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U2" t="n">
-        <v>251.3456529078368</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V2" t="n">
-        <v>327.7522584701353</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W2" t="n">
-        <v>349.2409687174135</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X2" t="n">
-        <v>369.7311006784697</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y2" t="n">
-        <v>386.2379386560542</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="3">
@@ -27380,25 +27380,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>166.5331836498676</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C3" t="n">
-        <v>172.708498988316</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D3" t="n">
-        <v>147.445065564639</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E3" t="n">
-        <v>157.6450804554012</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F3" t="n">
-        <v>145.0692123933841</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G3" t="n">
-        <v>137.3435171632109</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H3" t="n">
-        <v>112.2354442364967</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I3" t="n">
         <v>89.39663285141508</v>
@@ -27431,25 +27431,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S3" t="n">
-        <v>171.6831711038381</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T3" t="n">
-        <v>200.1647286948221</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U3" t="n">
-        <v>225.9413820809755</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V3" t="n">
-        <v>232.800587149426</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W3" t="n">
-        <v>251.6949831609203</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X3" t="n">
-        <v>205.772985203478</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y3" t="n">
-        <v>205.6826957773049</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="4">
@@ -27459,28 +27459,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179.8319801819375</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C4" t="n">
-        <v>167.246821098628</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D4" t="n">
-        <v>148.6154730182125</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E4" t="n">
-        <v>146.4339626465693</v>
+        <v>146.4339626465692</v>
       </c>
       <c r="F4" t="n">
-        <v>145.4210480229314</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G4" t="n">
-        <v>167.9909793584589</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H4" t="n">
-        <v>162.2271725074398</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I4" t="n">
-        <v>155.4504749272584</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J4" t="n">
         <v>93.35918011667277</v>
@@ -27507,28 +27507,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R4" t="n">
-        <v>177.2933913771696</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S4" t="n">
-        <v>224.0165980369725</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T4" t="n">
-        <v>227.9455894282817</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U4" t="n">
-        <v>286.3190293564914</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V4" t="n">
-        <v>252.1376433238285</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W4" t="n">
-        <v>286.5229983365915</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X4" t="n">
-        <v>225.7096553890374</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y4" t="n">
-        <v>218.5846533520951</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="5">
@@ -27538,28 +27538,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>382.7338416634817</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C5" t="n">
-        <v>365.2728917710086</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D5" t="n">
-        <v>354.6830416206842</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E5" t="n">
-        <v>381.9303700722627</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F5" t="n">
-        <v>400.0000000000001</v>
+        <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>400.0000000000001</v>
+        <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>339.4748021157684</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I5" t="n">
-        <v>210.4758895704069</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J5" t="n">
         <v>11.94928935461252</v>
@@ -27589,25 +27589,25 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S5" t="n">
-        <v>209.0200695862457</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T5" t="n">
-        <v>223.095849564132</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U5" t="n">
-        <v>251.3456529078374</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V5" t="n">
-        <v>327.752258470136</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W5" t="n">
-        <v>349.2409687174143</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X5" t="n">
-        <v>369.7311006784702</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y5" t="n">
-        <v>386.2379386560544</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="6">
@@ -27617,25 +27617,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>166.5331836498676</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C6" t="n">
-        <v>172.708498988316</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D6" t="n">
-        <v>147.445065564639</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E6" t="n">
-        <v>157.6450804554012</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F6" t="n">
-        <v>145.069212393384</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G6" t="n">
-        <v>137.3435171632108</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H6" t="n">
-        <v>112.2354442364967</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I6" t="n">
         <v>89.39663285141508</v>
@@ -27668,25 +27668,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S6" t="n">
-        <v>171.683171103838</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T6" t="n">
-        <v>200.1647286948219</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U6" t="n">
-        <v>225.9413820809751</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V6" t="n">
-        <v>232.8005871494256</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W6" t="n">
-        <v>251.6949831609199</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X6" t="n">
-        <v>205.7729852034777</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y6" t="n">
-        <v>205.6826957773047</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="7">
@@ -27696,10 +27696,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>179.8319801819374</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C7" t="n">
-        <v>167.2468210986279</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D7" t="n">
         <v>148.6154730182124</v>
@@ -27708,13 +27708,13 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F7" t="n">
-        <v>145.4210480229313</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G7" t="n">
         <v>167.9909793584588</v>
       </c>
       <c r="H7" t="n">
-        <v>162.2271725074397</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I7" t="n">
         <v>155.4504749272583</v>
@@ -27747,25 +27747,25 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S7" t="n">
-        <v>224.0165980369724</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T7" t="n">
-        <v>227.9455894282816</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U7" t="n">
-        <v>286.319029356491</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V7" t="n">
-        <v>252.1376433238281</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W7" t="n">
-        <v>286.5229983365911</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X7" t="n">
-        <v>225.7096553890373</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y7" t="n">
-        <v>218.584653352095</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="8">
@@ -27775,28 +27775,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>382.7338416634807</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C8" t="n">
-        <v>365.2728917710077</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D8" t="n">
-        <v>354.6830416206831</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E8" t="n">
-        <v>381.9303700722619</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F8" t="n">
-        <v>400.0000000000001</v>
+        <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>400.0000000000001</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>339.4748021157673</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I8" t="n">
-        <v>210.475889570406</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
         <v>11.94928935461252</v>
@@ -27826,25 +27826,25 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S8" t="n">
-        <v>209.0200695862454</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T8" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U8" t="n">
-        <v>251.3456529078366</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V8" t="n">
-        <v>327.752258470135</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W8" t="n">
-        <v>349.2409687174131</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X8" t="n">
-        <v>369.7311006784691</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y8" t="n">
-        <v>386.2379386560538</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="9">
@@ -27854,22 +27854,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>166.5331836498674</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C9" t="n">
-        <v>172.7084989883158</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D9" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E9" t="n">
-        <v>157.645080455401</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F9" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>137.3435171632107</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H9" t="n">
         <v>112.2354442364965</v>
@@ -27905,19 +27905,19 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S9" t="n">
-        <v>171.6831711038379</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T9" t="n">
-        <v>200.1647286948217</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U9" t="n">
-        <v>225.9413820809749</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V9" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W9" t="n">
-        <v>251.6949831609197</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X9" t="n">
         <v>205.7729852034775</v>
@@ -27933,10 +27933,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>179.8319801819374</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C10" t="n">
-        <v>167.2468210986279</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D10" t="n">
         <v>148.6154730182124</v>
@@ -27945,7 +27945,7 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F10" t="n">
-        <v>145.4210480229313</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
         <v>167.9909793584588</v>
@@ -27987,22 +27987,22 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T10" t="n">
-        <v>227.9455894282816</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U10" t="n">
         <v>286.3190293564909</v>
       </c>
       <c r="V10" t="n">
-        <v>252.1376433238281</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W10" t="n">
-        <v>286.5229983365911</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X10" t="n">
         <v>225.7096553890372</v>
       </c>
       <c r="Y10" t="n">
-        <v>218.5846533520949</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="11">
@@ -28012,28 +28012,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="J11" t="n">
         <v>11.94928935461252</v>
@@ -28060,28 +28060,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="T11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="U11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="V11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="W11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="Y11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
     </row>
     <row r="12">
@@ -28091,28 +28091,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="E12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="H12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="I12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="J12" t="n">
         <v>0.7465913262578567</v>
@@ -28139,28 +28139,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="T12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="U12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="V12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="W12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="Y12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
     </row>
     <row r="13">
@@ -28170,34 +28170,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="G13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="H13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="J13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -28215,31 +28215,31 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="R13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="T13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="U13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="V13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="W13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="X13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="Y13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
     </row>
     <row r="14">
@@ -28249,28 +28249,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J14" t="n">
         <v>11.94928935461252</v>
@@ -28297,28 +28297,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="15">
@@ -28328,25 +28328,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I15" t="n">
         <v>89.39663285141508</v>
@@ -28376,28 +28376,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="16">
@@ -28407,31 +28407,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J16" t="n">
-        <v>92.99999999999997</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
         <v>22.26949182588285</v>
@@ -28455,28 +28455,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="17">
@@ -28486,28 +28486,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -28534,28 +28534,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="18">
@@ -28565,25 +28565,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I18" t="n">
         <v>89.39663285141508</v>
@@ -28613,28 +28613,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="19">
@@ -28644,31 +28644,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J19" t="n">
-        <v>93.00000000000001</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K19" t="n">
         <v>22.26949182588285</v>
@@ -28692,28 +28692,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="20">
@@ -28723,28 +28723,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J20" t="n">
         <v>11.94928935461252</v>
@@ -28771,28 +28771,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="21">
@@ -28802,25 +28802,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I21" t="n">
         <v>89.39663285141508</v>
@@ -28850,28 +28850,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="22">
@@ -28881,31 +28881,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K22" t="n">
         <v>22.26949182588285</v>
@@ -28929,28 +28929,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="23">
@@ -28960,28 +28960,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J23" t="n">
         <v>11.94928935461252</v>
@@ -29008,28 +29008,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="24">
@@ -29039,25 +29039,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I24" t="n">
         <v>89.39663285141508</v>
@@ -29087,28 +29087,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="25">
@@ -29118,31 +29118,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J25" t="n">
-        <v>93.00000000000003</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K25" t="n">
         <v>22.26949182588285</v>
@@ -29166,28 +29166,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="26">
@@ -29197,28 +29197,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J26" t="n">
         <v>11.94928935461252</v>
@@ -29245,28 +29245,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="27">
@@ -29276,28 +29276,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
         <v>0.7465913262578567</v>
@@ -29324,28 +29324,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="28">
@@ -29355,31 +29355,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K28" t="n">
         <v>22.26949182588285</v>
@@ -29403,28 +29403,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="29">
@@ -29434,28 +29434,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="C29" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="D29" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="E29" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="F29" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="G29" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="H29" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="I29" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="J29" t="n">
         <v>11.94928935461252</v>
@@ -29482,28 +29482,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="S29" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="T29" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="U29" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="V29" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="W29" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="X29" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="Y29" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
     </row>
     <row r="30">
@@ -29513,19 +29513,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="C30" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="D30" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="E30" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="F30" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="G30" t="n">
         <v>137.3435171632106</v>
@@ -29561,28 +29561,28 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>100.1578341526434</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="T30" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="U30" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="V30" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="W30" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="X30" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="Y30" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
     </row>
     <row r="31">
@@ -29592,28 +29592,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="C31" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="D31" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="E31" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="F31" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="G31" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="H31" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="I31" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="J31" t="n">
         <v>93.35918011667277</v>
@@ -29640,28 +29640,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R31" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="S31" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="T31" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="U31" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="V31" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="W31" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="X31" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="Y31" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
     </row>
     <row r="32">
@@ -29671,28 +29671,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="C32" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="D32" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="E32" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="F32" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="G32" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="H32" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="I32" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="J32" t="n">
         <v>11.94928935461252</v>
@@ -29719,28 +29719,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="S32" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="T32" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="U32" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="V32" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="W32" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="X32" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="Y32" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
     </row>
     <row r="33">
@@ -29750,19 +29750,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="C33" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="D33" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="E33" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="F33" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="G33" t="n">
         <v>137.3435171632106</v>
@@ -29798,28 +29798,28 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526437</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="T33" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="U33" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="V33" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="W33" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="X33" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="Y33" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
     </row>
     <row r="34">
@@ -29829,28 +29829,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="C34" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="D34" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="E34" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="F34" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="G34" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="H34" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="I34" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="J34" t="n">
         <v>93.35918011667277</v>
@@ -29877,28 +29877,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="S34" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="T34" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="U34" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="V34" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="W34" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="X34" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="Y34" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
     </row>
     <row r="35">
@@ -29908,28 +29908,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="C35" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="D35" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="E35" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="F35" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="G35" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="H35" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="I35" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="J35" t="n">
         <v>11.94928935461252</v>
@@ -29956,28 +29956,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="S35" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="T35" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="U35" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="V35" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="W35" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="X35" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="Y35" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
     </row>
     <row r="36">
@@ -29987,19 +29987,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="C36" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="D36" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="E36" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="F36" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="G36" t="n">
         <v>137.3435171632106</v>
@@ -30038,25 +30038,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="T36" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="U36" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="V36" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="W36" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="X36" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="Y36" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
     </row>
     <row r="37">
@@ -30066,28 +30066,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="C37" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="D37" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="E37" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="F37" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="G37" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="H37" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="I37" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="J37" t="n">
         <v>93.35918011667277</v>
@@ -30114,28 +30114,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="S37" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="T37" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="U37" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="V37" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="W37" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="X37" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="Y37" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
     </row>
     <row r="38">
@@ -30145,28 +30145,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="C38" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="D38" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="E38" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="F38" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="G38" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="H38" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="I38" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="J38" t="n">
         <v>11.94928935461252</v>
@@ -30193,28 +30193,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="S38" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="T38" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="U38" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="V38" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="W38" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="X38" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="Y38" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
     </row>
     <row r="39">
@@ -30224,19 +30224,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="C39" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="D39" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="E39" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="F39" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="G39" t="n">
         <v>137.3435171632106</v>
@@ -30275,25 +30275,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="T39" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="U39" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="V39" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="W39" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="X39" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="Y39" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
     </row>
     <row r="40">
@@ -30303,28 +30303,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="C40" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="D40" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="E40" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="F40" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="G40" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="H40" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="I40" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="J40" t="n">
         <v>93.35918011667277</v>
@@ -30351,28 +30351,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="S40" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="T40" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="U40" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="V40" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="W40" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="X40" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
       <c r="Y40" t="n">
-        <v>142</v>
+        <v>141.6644489965123</v>
       </c>
     </row>
     <row r="41">
@@ -30382,28 +30382,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="C41" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="D41" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="E41" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="F41" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="G41" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="H41" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="I41" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="J41" t="n">
         <v>11.94928935461252</v>
@@ -30430,28 +30430,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="S41" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="T41" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="U41" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="V41" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="W41" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="X41" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="Y41" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
     </row>
     <row r="42">
@@ -30461,22 +30461,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="C42" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="D42" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="E42" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="F42" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="G42" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="H42" t="n">
         <v>112.2354442364965</v>
@@ -30512,25 +30512,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="T42" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="U42" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="V42" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="W42" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="X42" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="Y42" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
     </row>
     <row r="43">
@@ -30540,28 +30540,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="C43" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="D43" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="E43" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="F43" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="G43" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="H43" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="I43" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="J43" t="n">
         <v>93.35918011667277</v>
@@ -30588,28 +30588,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="S43" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="T43" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="U43" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="V43" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="W43" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="X43" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
       <c r="Y43" t="n">
-        <v>134</v>
+        <v>133.6777069071575</v>
       </c>
     </row>
     <row r="44">
